--- a/output/trucks.xlsx
+++ b/output/trucks.xlsx
@@ -505,7 +505,7 @@
         <v>46089</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -521,7 +521,7 @@
         <v>46091</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
